--- a/artfynd/A 24684-2026 artfynd.xlsx
+++ b/artfynd/A 24684-2026 artfynd.xlsx
@@ -3366,7 +3366,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133997430</v>
+        <v>133997422</v>
       </c>
       <c r="B26" t="n">
         <v>99181</v>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>637820</v>
+        <v>638036</v>
       </c>
       <c r="R26" t="n">
-        <v>6667522</v>
+        <v>6667444</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3482,7 +3482,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133997422</v>
+        <v>133997430</v>
       </c>
       <c r="B27" t="n">
         <v>99181</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>638036</v>
+        <v>637820</v>
       </c>
       <c r="R27" t="n">
-        <v>6667444</v>
+        <v>6667522</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 24684-2026 artfynd.xlsx
+++ b/artfynd/A 24684-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133997417</v>
       </c>
       <c r="B2" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>133997427</v>
       </c>
       <c r="B4" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>133997413</v>
       </c>
       <c r="B7" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>133997416</v>
       </c>
       <c r="B9" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>133997442</v>
       </c>
       <c r="B10" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>133997448</v>
       </c>
       <c r="B12" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>133997423</v>
       </c>
       <c r="B15" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>133997412</v>
       </c>
       <c r="B16" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>133997426</v>
       </c>
       <c r="B17" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>133997445</v>
       </c>
       <c r="B19" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>133997439</v>
       </c>
       <c r="B21" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>133997447</v>
       </c>
       <c r="B22" t="n">
-        <v>99085</v>
+        <v>99092</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3366,10 +3366,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133997422</v>
+        <v>133997430</v>
       </c>
       <c r="B26" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>638036</v>
+        <v>637820</v>
       </c>
       <c r="R26" t="n">
-        <v>6667444</v>
+        <v>6667522</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3482,10 +3482,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133997430</v>
+        <v>133997422</v>
       </c>
       <c r="B27" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>637820</v>
+        <v>638036</v>
       </c>
       <c r="R27" t="n">
-        <v>6667522</v>
+        <v>6667444</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 24684-2026 artfynd.xlsx
+++ b/artfynd/A 24684-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133997417</v>
+        <v>133997436</v>
       </c>
       <c r="B2" t="n">
-        <v>99188</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>S om Bråboda mosse, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638009</v>
+        <v>637718</v>
       </c>
       <c r="R2" t="n">
-        <v>6667478</v>
+        <v>6667523</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133997443</v>
+        <v>133997441</v>
       </c>
       <c r="B3" t="n">
-        <v>5181</v>
+        <v>97435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637754</v>
+        <v>637744</v>
       </c>
       <c r="R3" t="n">
-        <v>6667513</v>
+        <v>6667507</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,54 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133997427</v>
+        <v>133997420</v>
       </c>
       <c r="B4" t="n">
-        <v>99188</v>
+        <v>96410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>S om Bråboda mosse, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637792</v>
+        <v>638060</v>
       </c>
       <c r="R4" t="n">
-        <v>6667520</v>
+        <v>6667436</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -977,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133997409</v>
+        <v>133997407</v>
       </c>
       <c r="B5" t="n">
-        <v>5181</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637935</v>
+        <v>637881</v>
       </c>
       <c r="R5" t="n">
-        <v>6667569</v>
+        <v>6667606</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133997428</v>
+        <v>133997411</v>
       </c>
       <c r="B6" t="n">
-        <v>8449</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,37 +1114,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>S om Bråboda mosse, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637798</v>
+        <v>637973</v>
       </c>
       <c r="R6" t="n">
-        <v>6667529</v>
+        <v>6667508</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,42 +1215,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133997413</v>
+        <v>133997414</v>
       </c>
       <c r="B7" t="n">
-        <v>99188</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1272,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637989</v>
+        <v>637994</v>
       </c>
       <c r="R7" t="n">
-        <v>6667505</v>
+        <v>6667501</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1317,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133997410</v>
+        <v>133997425</v>
       </c>
       <c r="B8" t="n">
-        <v>8449</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1379,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637944</v>
+        <v>637768</v>
       </c>
       <c r="R8" t="n">
-        <v>6667575</v>
+        <v>6667502</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1414,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1424,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,42 +1434,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133997416</v>
+        <v>133997432</v>
       </c>
       <c r="B9" t="n">
-        <v>99188</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1495,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>638004</v>
+        <v>637749</v>
       </c>
       <c r="R9" t="n">
-        <v>6667481</v>
+        <v>6667557</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1530,7 +1509,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1540,7 +1519,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,42 +1546,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133997442</v>
+        <v>133997437</v>
       </c>
       <c r="B10" t="n">
-        <v>99188</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1611,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>637754</v>
+        <v>637719</v>
       </c>
       <c r="R10" t="n">
-        <v>6667512</v>
+        <v>6667539</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1646,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1631,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,32 +1658,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133997425</v>
+        <v>133997405</v>
       </c>
       <c r="B11" t="n">
-        <v>57972</v>
+        <v>5181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637768</v>
+        <v>637858</v>
       </c>
       <c r="R11" t="n">
-        <v>6667502</v>
+        <v>6667546</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1753,7 +1728,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1738,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,54 +1765,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133997448</v>
+        <v>133997408</v>
       </c>
       <c r="B12" t="n">
-        <v>99188</v>
+        <v>5181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>S om Bråboda mosse, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637846</v>
+        <v>637888</v>
       </c>
       <c r="R12" t="n">
-        <v>6667453</v>
+        <v>6667609</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1869,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1879,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133997435</v>
+        <v>133997409</v>
       </c>
       <c r="B13" t="n">
-        <v>4782</v>
+        <v>5181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1917,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>637732</v>
+        <v>637935</v>
       </c>
       <c r="R13" t="n">
-        <v>6667527</v>
+        <v>6667569</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1976,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1986,7 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2013,50 +1979,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133997437</v>
+        <v>133997443</v>
       </c>
       <c r="B14" t="n">
-        <v>57972</v>
+        <v>5181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>S om Bråboda mosse, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>637719</v>
+        <v>637754</v>
       </c>
       <c r="R14" t="n">
-        <v>6667539</v>
+        <v>6667513</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2088,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2098,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2125,54 +2086,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133997423</v>
+        <v>133997434</v>
       </c>
       <c r="B15" t="n">
-        <v>99188</v>
+        <v>4782</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>S om Bråboda mosse, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>637788</v>
+        <v>637729</v>
       </c>
       <c r="R15" t="n">
-        <v>6667470</v>
+        <v>6667529</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2204,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2214,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,57 +2193,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133997412</v>
+        <v>133997435</v>
       </c>
       <c r="B16" t="n">
-        <v>99188</v>
+        <v>4782</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>S om Bråboda mosse, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>637986</v>
+        <v>637732</v>
       </c>
       <c r="R16" t="n">
-        <v>6667513</v>
+        <v>6667527</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2320,7 +2263,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2330,7 +2273,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2357,54 +2300,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133997426</v>
+        <v>133997440</v>
       </c>
       <c r="B17" t="n">
-        <v>99188</v>
+        <v>4782</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>S om Bråboda mosse, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>637785</v>
+        <v>637744</v>
       </c>
       <c r="R17" t="n">
-        <v>6667498</v>
+        <v>6667504</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2436,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2446,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2580,54 +2514,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133997445</v>
+        <v>133997406</v>
       </c>
       <c r="B19" t="n">
-        <v>99188</v>
+        <v>8449</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>S om Bråboda mosse, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>637804</v>
+        <v>637884</v>
       </c>
       <c r="R19" t="n">
-        <v>6667517</v>
+        <v>6667592</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2659,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,7 +2621,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133997438</v>
+        <v>133997410</v>
       </c>
       <c r="B20" t="n">
         <v>8449</v>
@@ -2731,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>637720</v>
+        <v>637944</v>
       </c>
       <c r="R20" t="n">
-        <v>6667541</v>
+        <v>6667575</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2766,7 +2691,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2701,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,54 +2728,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133997439</v>
+        <v>133997424</v>
       </c>
       <c r="B21" t="n">
-        <v>99188</v>
+        <v>8449</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>S om Bråboda mosse, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>637772</v>
+        <v>637773</v>
       </c>
       <c r="R21" t="n">
-        <v>6667506</v>
+        <v>6667476</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2882,7 +2798,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2892,7 +2808,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133997447</v>
+        <v>133997428</v>
       </c>
       <c r="B22" t="n">
-        <v>99092</v>
+        <v>8449</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,43 +2846,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220093</v>
+        <v>106554</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>S om Bråboda mosse, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>637866</v>
+        <v>637798</v>
       </c>
       <c r="R22" t="n">
-        <v>6667436</v>
+        <v>6667529</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2998,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3008,7 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3035,53 +2942,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133997414</v>
+        <v>133997438</v>
       </c>
       <c r="B23" t="n">
-        <v>57972</v>
+        <v>8449</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>S om Bråboda mosse, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>637994</v>
+        <v>637720</v>
       </c>
       <c r="R23" t="n">
-        <v>6667501</v>
+        <v>6667541</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3110,7 +3012,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3120,7 +3022,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3147,10 +3049,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133997405</v>
+        <v>133997447</v>
       </c>
       <c r="B24" t="n">
-        <v>5181</v>
+        <v>99099</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3158,34 +3060,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>220093</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>S om Bråboda mosse, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>637858</v>
+        <v>637866</v>
       </c>
       <c r="R24" t="n">
-        <v>6667546</v>
+        <v>6667436</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3217,7 +3128,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3227,7 +3138,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3254,38 +3165,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133997411</v>
+        <v>133997412</v>
       </c>
       <c r="B25" t="n">
-        <v>57972</v>
+        <v>99195</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3294,13 +3209,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>637973</v>
+        <v>637986</v>
       </c>
       <c r="R25" t="n">
-        <v>6667508</v>
+        <v>6667513</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3329,7 +3244,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3339,7 +3254,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3366,10 +3281,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133997430</v>
+        <v>133997413</v>
       </c>
       <c r="B26" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3396,7 +3311,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3410,10 +3325,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>637820</v>
+        <v>637989</v>
       </c>
       <c r="R26" t="n">
-        <v>6667522</v>
+        <v>6667505</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3445,7 +3360,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3455,7 +3370,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3482,10 +3397,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133997422</v>
+        <v>133997416</v>
       </c>
       <c r="B27" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3512,7 +3427,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3526,10 +3441,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>638036</v>
+        <v>638004</v>
       </c>
       <c r="R27" t="n">
-        <v>6667444</v>
+        <v>6667481</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3561,7 +3476,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3571,7 +3486,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3595,6 +3510,1272 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>133997417</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>S om Bråboda mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>638009</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6667478</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>133997422</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>S om Bråboda mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>638036</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6667444</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133997423</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>S om Bråboda mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>637788</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6667470</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133997426</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>S om Bråboda mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>637785</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6667498</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133997427</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>S om Bråboda mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>637792</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6667520</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133997430</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>S om Bråboda mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>637820</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6667522</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>133997439</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>S om Bråboda mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>637772</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6667506</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>133997442</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>S om Bråboda mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>637754</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6667512</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>133997445</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>S om Bråboda mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>637804</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6667517</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>133997448</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>S om Bråboda mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>637846</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6667453</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>133997433</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91993</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6332881</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>S om Bråboda mosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>637728</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6667528</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Viksta</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
